--- a/flying/sim_results_edited.xlsx
+++ b/flying/sim_results_edited.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="sim_results (cópia)" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,6 +21,8 @@
     <sheet name="P2" sheetId="11" state="visible" r:id="rId12"/>
     <sheet name="Planilha10" sheetId="12" state="visible" r:id="rId13"/>
     <sheet name="Planilha11" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="Planilha10_2" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="Planilha11_2" sheetId="15" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="113">
   <si>
     <t xml:space="preserve">l2_error</t>
   </si>
@@ -100,15 +102,195 @@
     <t xml:space="preserve">brazilC2</t>
   </si>
   <si>
+    <t xml:space="preserve">4.202740106373468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8397182769403757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423259058657071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0782621971274329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0177510096199239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.55008787346221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82621971274329</t>
+  </si>
+  <si>
     <t xml:space="preserve">crossf</t>
   </si>
   <si>
     <t xml:space="preserve">crossC2</t>
   </si>
   <si>
+    <t xml:space="preserve">16.98465007111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.272080146348681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8081312507320355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1163035861335987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.049449831463592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.690685413005272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.630358613359872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.026317524063286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7822493986382817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7657087585258546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1160946149880279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0592426110108911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.33216168717048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6094614988028</t>
+  </si>
+  <si>
     <t xml:space="preserve">crossC1</t>
   </si>
   <si>
+    <t xml:space="preserve">41.605567360300135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32076599632037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6966215077702156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1989889802270791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1211322155770212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.34797891036907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.89889802270791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.731528372831264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.728128089928222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7350844662939133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1122771009357804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0579975173512967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.579964850615114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.227710093578043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.13633351779807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71063039600913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.573830959525976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2086100341765334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108120298383683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.731107205623902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.86100341765334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.422462224583068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6815605095344519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3999447365772361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0739512909975233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0144553691959846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.66256590509666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.395129099752339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3219844088088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0378176877494134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7395394391840195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10988185882717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04460907604991731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.724077328646749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.988185882717316</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brasil (alpha=0.1)</t>
   </si>
   <si>
@@ -154,13 +336,40 @@
     <t xml:space="preserve">Alpha=0.5</t>
   </si>
   <si>
-    <t xml:space="preserve">Cross</t>
+    <t xml:space="preserve">Coarse 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unstructured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross (alpha=0.1)</t>
   </si>
   <si>
     <t xml:space="preserve">Coarse 1 (structured)</t>
   </si>
   <si>
     <t xml:space="preserve">Coarse2 (unstructured)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barreira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K = 0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K = 1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha = 0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross (alpha=0.5)</t>
   </si>
   <si>
     <t xml:space="preserve">Erro Absoluto</t>
@@ -180,6 +389,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -199,13 +409,14 @@
     <font>
       <sz val="21"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -309,9 +520,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>61560</xdr:colOff>
+      <xdr:colOff>61200</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>114120</xdr:rowOff>
+      <xdr:rowOff>113760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -324,8 +535,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2797920" y="162360"/>
-          <a:ext cx="5391720" cy="3528000"/>
+          <a:off x="2801880" y="162360"/>
+          <a:ext cx="5400000" cy="3527640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -346,9 +557,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>687960</xdr:colOff>
+      <xdr:colOff>687600</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>141480</xdr:rowOff>
+      <xdr:rowOff>141120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -361,8 +572,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="985680" y="3928680"/>
-          <a:ext cx="5391720" cy="3528000"/>
+          <a:off x="986760" y="3928680"/>
+          <a:ext cx="5399280" cy="3527640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -383,9 +594,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>728280</xdr:colOff>
+      <xdr:colOff>727920</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>32040</xdr:rowOff>
+      <xdr:rowOff>31680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -398,8 +609,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6715800" y="3981960"/>
-          <a:ext cx="5391720" cy="3528000"/>
+          <a:off x="6725880" y="3981960"/>
+          <a:ext cx="5398920" cy="3527640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -420,19 +631,19 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>279720</xdr:colOff>
+      <xdr:colOff>279360</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>162360</xdr:rowOff>
+      <xdr:rowOff>162000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="Quadro de texto 1"/>
-        <xdr:cNvSpPr txBox="1"/>
+        <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2118600" y="1422360"/>
-          <a:ext cx="599400" cy="365760"/>
+          <a:off x="2121120" y="1422360"/>
+          <a:ext cx="600480" cy="365400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -442,11 +653,22 @@
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
       <xdr:txBody>
         <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="pt-BR" sz="2100" spc="-1" strike="noStrike">
               <a:latin typeface="Times New Roman"/>
@@ -470,19 +692,19 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>679320</xdr:colOff>
+      <xdr:colOff>678960</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>40680</xdr:rowOff>
+      <xdr:rowOff>40320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="Quadro de texto 2"/>
-        <xdr:cNvSpPr txBox="1"/>
+        <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8208000" y="1300680"/>
-          <a:ext cx="599400" cy="365760"/>
+          <a:off x="8220600" y="1300680"/>
+          <a:ext cx="599040" cy="365400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -492,11 +714,22 @@
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
       <xdr:txBody>
         <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="pt-BR" sz="2100" spc="-1" strike="noStrike">
               <a:latin typeface="Times New Roman"/>
@@ -520,19 +753,19 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>279720</xdr:colOff>
+      <xdr:colOff>279360</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>108360</xdr:rowOff>
+      <xdr:rowOff>108000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="Quadro de texto 3"/>
-        <xdr:cNvSpPr txBox="1"/>
+        <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5236560" y="1693440"/>
-          <a:ext cx="732600" cy="365760"/>
+          <a:off x="5244120" y="1693440"/>
+          <a:ext cx="733680" cy="365400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -542,22 +775,27 @@
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
       <xdr:txBody>
         <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="pt-BR" sz="2100" spc="-1" strike="noStrike">
               <a:latin typeface="Times New Roman"/>
             </a:rPr>
-            <a:t>P=0.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr b="0" lang="pt-BR" sz="2100" spc="-1" strike="noStrike">
-              <a:latin typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>5</a:t>
+            <a:t>P=0.5</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="pt-BR" sz="2100" spc="-1" strike="noStrike">
             <a:latin typeface="Times New Roman"/>
@@ -581,9 +819,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>402840</xdr:colOff>
+      <xdr:colOff>402480</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>113760</xdr:rowOff>
+      <xdr:rowOff>113400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -597,7 +835,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="585360" y="1797120"/>
-          <a:ext cx="7607160" cy="1730520"/>
+          <a:ext cx="7616880" cy="1730160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -618,9 +856,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>208080</xdr:colOff>
+      <xdr:colOff>207720</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -629,8 +867,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2396880" y="2773080"/>
-          <a:ext cx="723960" cy="621360"/>
+          <a:off x="2399400" y="2773080"/>
+          <a:ext cx="723600" cy="621000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -661,9 +899,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>782280</xdr:colOff>
+      <xdr:colOff>781920</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>9000</xdr:rowOff>
+      <xdr:rowOff>8640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -672,8 +910,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3783960" y="2801520"/>
-          <a:ext cx="723960" cy="621360"/>
+          <a:off x="3787560" y="2801520"/>
+          <a:ext cx="723600" cy="621000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -704,9 +942,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>68400</xdr:colOff>
+      <xdr:colOff>68040</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -715,8 +953,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5508360" y="2773080"/>
-          <a:ext cx="723960" cy="621360"/>
+          <a:off x="5514840" y="2773080"/>
+          <a:ext cx="724680" cy="621000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -747,9 +985,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>217440</xdr:colOff>
+      <xdr:colOff>217080</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -758,8 +996,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7283160" y="2773080"/>
-          <a:ext cx="723960" cy="621360"/>
+          <a:off x="7292160" y="2773080"/>
+          <a:ext cx="724680" cy="621000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -790,9 +1028,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>342000</xdr:colOff>
+      <xdr:colOff>341640</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>162360</xdr:rowOff>
+      <xdr:rowOff>162000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -805,8 +1043,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1316520" y="3643200"/>
-          <a:ext cx="6002280" cy="745560"/>
+          <a:off x="1317600" y="3643200"/>
+          <a:ext cx="6009840" cy="745200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -820,16 +1058,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>586800</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>546480</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>92160</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>26280</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>41040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>799920</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>132480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -842,8 +1080,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9189000" y="162720"/>
-          <a:ext cx="4023720" cy="2855520"/>
+          <a:off x="10268280" y="691200"/>
+          <a:ext cx="4029840" cy="2855160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -857,16 +1095,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>172080</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>360</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>93600</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>154440</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>92160</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>122400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>13680</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>113400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -879,8 +1117,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8774280" y="3089160"/>
-          <a:ext cx="4798440" cy="3405240"/>
+          <a:off x="15218640" y="122400"/>
+          <a:ext cx="4805640" cy="3404880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -900,15 +1138,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>279720</xdr:colOff>
+      <xdr:colOff>440280</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>27000</xdr:rowOff>
+      <xdr:rowOff>149040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>452880</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>70200</xdr:rowOff>
+      <xdr:colOff>787320</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>19800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -921,8 +1159,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="279720" y="352080"/>
-          <a:ext cx="5050080" cy="2969280"/>
+          <a:off x="440280" y="474120"/>
+          <a:ext cx="5231520" cy="3772080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -936,16 +1174,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>666360</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>149040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>170280</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>43560</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>547560</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>414000</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>89640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -958,8 +1196,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666360" y="3888000"/>
-          <a:ext cx="3567960" cy="3470760"/>
+          <a:off x="1361520" y="4714200"/>
+          <a:ext cx="3936960" cy="3665880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -974,15 +1212,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>399960</xdr:colOff>
+      <xdr:colOff>39960</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>54720</xdr:rowOff>
+      <xdr:rowOff>81720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>630720</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>108360</xdr:rowOff>
+      <xdr:colOff>53280</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -995,8 +1233,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6902280" y="379800"/>
-          <a:ext cx="5107680" cy="2979720"/>
+          <a:off x="6552360" y="406800"/>
+          <a:ext cx="4897800" cy="3511800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1010,16 +1248,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>746640</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>613440</xdr:colOff>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>135360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>290160</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>68400</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>738000</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>133200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1032,8 +1270,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8061840" y="3874320"/>
-          <a:ext cx="3607560" cy="3509280"/>
+          <a:off x="7125840" y="4524480"/>
+          <a:ext cx="4195080" cy="3899160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1052,20 +1290,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>666000</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>10440</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>483480</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>135720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>541440</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>78120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Figura 29" descr=""/>
+        <xdr:cNvPr id="51" name="Figura 30" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1074,8 +1312,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="812880" y="325080"/>
-          <a:ext cx="4730040" cy="2774160"/>
+          <a:off x="483480" y="3711960"/>
+          <a:ext cx="4128480" cy="3844080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1089,20 +1327,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>294120</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>386280</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>85680</xdr:rowOff>
+      <xdr:colOff>667440</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>30240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Figura 30" descr=""/>
+        <xdr:cNvPr id="52" name="Figura 29" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1111,8 +1349,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="812880" y="3738960"/>
-          <a:ext cx="3637440" cy="3499200"/>
+          <a:off x="294120" y="420120"/>
+          <a:ext cx="4443840" cy="3186360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1127,19 +1365,19 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>226800</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>81000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>266760</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>37080</xdr:rowOff>
+      <xdr:colOff>69480</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>27000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>443880</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>64800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Figura 31" descr=""/>
+        <xdr:cNvPr id="53" name="Figura 32" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1148,8 +1386,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5916240" y="243720"/>
-          <a:ext cx="4916880" cy="2882160"/>
+          <a:off x="5767920" y="3765960"/>
+          <a:ext cx="4444920" cy="4101840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1163,20 +1401,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>693000</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>13680</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>266400</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>99000</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>752400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>121680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>668520</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>159480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Figura 32" descr=""/>
+        <xdr:cNvPr id="54" name="Figura 31" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1185,8 +1423,314 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7195320" y="3915000"/>
-          <a:ext cx="3637440" cy="3499200"/>
+          <a:off x="5636880" y="121680"/>
+          <a:ext cx="4800600" cy="3451680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>807120</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>26640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>205200</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>105840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Figura 46" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6505560" y="4740840"/>
+          <a:ext cx="4282560" cy="3980520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>774720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>135360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>635040</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>40680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Figura 45" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6473160" y="135360"/>
+          <a:ext cx="5558760" cy="3969360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>404280</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>39960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>201240</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>77760</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Figura 44" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1218240" y="4754160"/>
+          <a:ext cx="3867480" cy="3614040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>13680</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>27360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>453960</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>111600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Figura 49" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="827640" y="352440"/>
+          <a:ext cx="5324760" cy="3823200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>360000</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>94680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>560160</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>149040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Figura 43" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6058440" y="94680"/>
+          <a:ext cx="5084640" cy="3630600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>223920</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>149040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>603000</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>132840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Figura 47" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6736320" y="3888000"/>
+          <a:ext cx="3635640" cy="3397320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>587160</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>41040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>626400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>162720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Figura 50" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="587160" y="366120"/>
+          <a:ext cx="4923720" cy="3535560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>39960</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>122040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>444240</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>24840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Figura 48" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="853920" y="4186080"/>
+          <a:ext cx="4474800" cy="4129200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1212,9 +1756,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>739800</xdr:colOff>
+      <xdr:colOff>739440</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>114480</xdr:rowOff>
+      <xdr:rowOff>114120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1228,7 +1772,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="237600" y="1635120"/>
-          <a:ext cx="6666120" cy="1730520"/>
+          <a:ext cx="6673320" cy="1730160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1249,9 +1793,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>424080</xdr:colOff>
+      <xdr:colOff>423720</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>114480</xdr:rowOff>
+      <xdr:rowOff>114120</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1260,8 +1804,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1902600" y="2581920"/>
-          <a:ext cx="621360" cy="621360"/>
+          <a:off x="1903680" y="2581920"/>
+          <a:ext cx="621360" cy="621000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1292,9 +1836,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>263520</xdr:colOff>
+      <xdr:colOff>263160</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>123480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1303,8 +1847,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3367800" y="2591280"/>
-          <a:ext cx="621360" cy="621360"/>
+          <a:off x="3370320" y="2591280"/>
+          <a:ext cx="622080" cy="621000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1335,9 +1879,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>46080</xdr:colOff>
+      <xdr:colOff>45720</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>123480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1346,8 +1890,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4775760" y="2591280"/>
-          <a:ext cx="621360" cy="621360"/>
+          <a:off x="4780800" y="2591280"/>
+          <a:ext cx="622440" cy="621000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1378,9 +1922,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>640440</xdr:colOff>
+      <xdr:colOff>640080</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>132840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1389,8 +1933,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6183000" y="2600640"/>
-          <a:ext cx="621360" cy="621360"/>
+          <a:off x="6190560" y="2600640"/>
+          <a:ext cx="621000" cy="621000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1421,9 +1965,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>281880</xdr:colOff>
+      <xdr:colOff>281520</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>75960</xdr:rowOff>
+      <xdr:rowOff>75600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1437,7 +1981,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="446400" y="3556800"/>
-          <a:ext cx="5999400" cy="745560"/>
+          <a:ext cx="6006600" cy="745200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1458,9 +2002,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>964080</xdr:colOff>
+      <xdr:colOff>963720</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>118800</xdr:rowOff>
+      <xdr:rowOff>118440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1473,8 +2017,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7194240" y="2790720"/>
-          <a:ext cx="4207320" cy="3017520"/>
+          <a:off x="7203240" y="2790720"/>
+          <a:ext cx="4210560" cy="3017160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1495,9 +2039,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>612720</xdr:colOff>
+      <xdr:colOff>612360</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>149040</xdr:rowOff>
+      <xdr:rowOff>148680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1510,8 +2054,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11415600" y="2790360"/>
-          <a:ext cx="4249800" cy="3048120"/>
+          <a:off x="11428200" y="2790360"/>
+          <a:ext cx="4254480" cy="3047760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1537,9 +2081,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>653760</xdr:colOff>
+      <xdr:colOff>653400</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>47160</xdr:rowOff>
+      <xdr:rowOff>46800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1553,7 +2097,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="277560" y="114480"/>
-          <a:ext cx="8504280" cy="3996720"/>
+          <a:ext cx="8516520" cy="3996360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1579,9 +2123,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>317160</xdr:colOff>
+      <xdr:colOff>316800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>102600</xdr:rowOff>
+      <xdr:rowOff>102240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1595,7 +2139,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="257760" y="172440"/>
-          <a:ext cx="3310560" cy="3181320"/>
+          <a:ext cx="3315240" cy="3180960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1616,9 +2160,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>612000</xdr:colOff>
+      <xdr:colOff>611640</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
+      <xdr:rowOff>18720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1631,8 +2175,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3813840" y="143640"/>
-          <a:ext cx="3300480" cy="3289320"/>
+          <a:off x="3818880" y="143640"/>
+          <a:ext cx="3305160" cy="3288960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1653,9 +2197,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>174960</xdr:colOff>
+      <xdr:colOff>174600</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>153360</xdr:rowOff>
+      <xdr:rowOff>153000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1668,8 +2212,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7447680" y="76320"/>
-          <a:ext cx="3293640" cy="3328200"/>
+          <a:off x="7459200" y="76320"/>
+          <a:ext cx="3298320" cy="3327840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1690,9 +2234,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>360000</xdr:colOff>
+      <xdr:colOff>359640</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>97200</xdr:rowOff>
+      <xdr:rowOff>96840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1705,8 +2249,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2935800" y="3887640"/>
-          <a:ext cx="3926520" cy="2549520"/>
+          <a:off x="2939760" y="3887640"/>
+          <a:ext cx="3932280" cy="2549160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1727,9 +2271,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>693360</xdr:colOff>
+      <xdr:colOff>693000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>15840</xdr:rowOff>
+      <xdr:rowOff>15480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1742,8 +2286,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8021880" y="3888000"/>
-          <a:ext cx="4050720" cy="2630160"/>
+          <a:off x="8033400" y="3888000"/>
+          <a:ext cx="4056480" cy="2629800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1764,14 +2308,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>119880</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>67680</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>148680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>66600</xdr:colOff>
+      <xdr:colOff>66240</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>161280</xdr:rowOff>
+      <xdr:rowOff>79560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1784,8 +2328,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="119880" y="392760"/>
-          <a:ext cx="4010760" cy="2531880"/>
+          <a:off x="119880" y="311400"/>
+          <a:ext cx="4016880" cy="2531520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1806,9 +2350,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>39960</xdr:colOff>
+      <xdr:colOff>39600</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>78480</xdr:rowOff>
+      <xdr:rowOff>78120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1821,8 +2365,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4650120" y="270720"/>
-          <a:ext cx="4330800" cy="2733840"/>
+          <a:off x="4656600" y="270720"/>
+          <a:ext cx="4337640" cy="2733480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1843,9 +2387,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>452520</xdr:colOff>
+      <xdr:colOff>452160</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>138960</xdr:rowOff>
+      <xdr:rowOff>138600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1858,8 +2402,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5716080" y="3576960"/>
-          <a:ext cx="3677400" cy="2414160"/>
+          <a:off x="5725080" y="3576960"/>
+          <a:ext cx="3681720" cy="2413800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1875,14 +2419,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>360000</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>40320</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>54000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>40320</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>60120</xdr:rowOff>
+      <xdr:colOff>39960</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>73080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1895,8 +2439,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="360000" y="3291480"/>
-          <a:ext cx="3744360" cy="2458080"/>
+          <a:off x="360000" y="3630240"/>
+          <a:ext cx="3750480" cy="2457720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1922,9 +2466,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>406080</xdr:colOff>
+      <xdr:colOff>405720</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>143640</xdr:rowOff>
+      <xdr:rowOff>143280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1938,7 +2482,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="208440" y="239400"/>
-          <a:ext cx="8325720" cy="3480480"/>
+          <a:ext cx="8337960" cy="3480120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1964,9 +2508,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>465840</xdr:colOff>
+      <xdr:colOff>465480</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>59400</xdr:rowOff>
+      <xdr:rowOff>59040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1980,7 +2524,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="214920" y="124920"/>
-          <a:ext cx="3502080" cy="3510720"/>
+          <a:ext cx="3506760" cy="3510360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2001,9 +2545,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>99000</xdr:colOff>
+      <xdr:colOff>98640</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>80640</xdr:rowOff>
+      <xdr:rowOff>80280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2016,8 +2560,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3794040" y="28080"/>
-          <a:ext cx="3620160" cy="3628800"/>
+          <a:off x="3799080" y="28080"/>
+          <a:ext cx="3626280" cy="3628440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2038,9 +2582,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>683640</xdr:colOff>
+      <xdr:colOff>683280</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>41400</xdr:rowOff>
+      <xdr:rowOff>41040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2053,8 +2597,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7641000" y="0"/>
-          <a:ext cx="3609000" cy="3617640"/>
+          <a:off x="7652520" y="0"/>
+          <a:ext cx="3613680" cy="3617280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2075,9 +2619,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>153720</xdr:colOff>
+      <xdr:colOff>153360</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>97560</xdr:rowOff>
+      <xdr:rowOff>97200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2090,8 +2634,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3438000" y="3983040"/>
-          <a:ext cx="4030920" cy="2616840"/>
+          <a:off x="3443040" y="3983040"/>
+          <a:ext cx="4037040" cy="2616480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2112,9 +2656,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>80640</xdr:colOff>
+      <xdr:colOff>80280</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>34560</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2127,8 +2671,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8235360" y="3915720"/>
-          <a:ext cx="4037400" cy="2621160"/>
+          <a:off x="8247960" y="3915720"/>
+          <a:ext cx="4043520" cy="2620800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2154,9 +2698,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>452880</xdr:colOff>
+      <xdr:colOff>452520</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>97920</xdr:rowOff>
+      <xdr:rowOff>97560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2170,7 +2714,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="199800" y="325080"/>
-          <a:ext cx="4317120" cy="2698920"/>
+          <a:ext cx="4323240" cy="2698560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2191,9 +2735,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>332640</xdr:colOff>
+      <xdr:colOff>332280</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>99360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2207,7 +2751,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="226440" y="3503880"/>
-          <a:ext cx="4170240" cy="2773080"/>
+          <a:ext cx="4176360" cy="2772720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2228,9 +2772,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>173160</xdr:colOff>
+      <xdr:colOff>172800</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>82800</xdr:rowOff>
+      <xdr:rowOff>82440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2243,8 +2787,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5809320" y="243720"/>
-          <a:ext cx="4117320" cy="2602440"/>
+          <a:off x="5818320" y="243720"/>
+          <a:ext cx="4123440" cy="2602080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2265,9 +2809,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>426240</xdr:colOff>
+      <xdr:colOff>425880</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>157320</xdr:rowOff>
+      <xdr:rowOff>156960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2280,8 +2824,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5649480" y="3540600"/>
-          <a:ext cx="4530240" cy="2956680"/>
+          <a:off x="5657040" y="3540600"/>
+          <a:ext cx="4537800" cy="2956320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2301,15 +2845,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>239760</xdr:colOff>
+      <xdr:colOff>587160</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>68040</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>516960</xdr:colOff>
+      <xdr:rowOff>67680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>50040</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>87120</xdr:rowOff>
+      <xdr:rowOff>86400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2322,8 +2866,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="239760" y="68040"/>
-          <a:ext cx="4341240" cy="4245480"/>
+          <a:off x="587160" y="67680"/>
+          <a:ext cx="4347360" cy="4245120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2338,15 +2882,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>66240</xdr:colOff>
+      <xdr:colOff>412920</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>13320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>343440</xdr:colOff>
+      <xdr:colOff>689760</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>32400</xdr:rowOff>
+      <xdr:rowOff>32040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2359,8 +2903,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4943160" y="176040"/>
-          <a:ext cx="4341240" cy="4245480"/>
+          <a:off x="5297400" y="176040"/>
+          <a:ext cx="4347000" cy="4245120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2374,16 +2918,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>666000</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>198360</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>94680</xdr:rowOff>
+      <xdr:rowOff>26640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>130680</xdr:colOff>
+      <xdr:colOff>477000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>113760</xdr:rowOff>
+      <xdr:rowOff>45360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2396,8 +2940,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9606960" y="257400"/>
-          <a:ext cx="4341240" cy="4245480"/>
+          <a:off x="9967320" y="189360"/>
+          <a:ext cx="4348800" cy="4245120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2412,25 +2956,25 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>120240</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>13320</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>719640</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>54000</xdr:rowOff>
+      <xdr:colOff>734040</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>53640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>519120</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>93600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="37" name="Quadro de texto 4"/>
-        <xdr:cNvSpPr txBox="1"/>
+        <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4184280" y="4402440"/>
-          <a:ext cx="599400" cy="365760"/>
+          <a:off x="4804560" y="4280040"/>
+          <a:ext cx="599040" cy="365400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2440,11 +2984,22 @@
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
       <xdr:txBody>
         <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="pt-BR" sz="2100" spc="-1" strike="noStrike">
               <a:latin typeface="Times New Roman"/>
@@ -2462,25 +3017,25 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>133560</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>13680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>599400</xdr:colOff>
+      <xdr:colOff>732600</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>54360</xdr:rowOff>
+      <xdr:rowOff>54000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="38" name="Quadro de texto 5"/>
-        <xdr:cNvSpPr txBox="1"/>
+        <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="13680"/>
-          <a:ext cx="599400" cy="365760"/>
+          <a:off x="133560" y="13680"/>
+          <a:ext cx="599040" cy="365400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2490,16 +3045,27 @@
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
       <xdr:txBody>
         <a:bodyPr lIns="0" rIns="0" tIns="0" bIns="0" anchor="t">
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="pt-BR" sz="2100" spc="-1" strike="noStrike">
               <a:latin typeface="Times New Roman"/>
             </a:rPr>
-            <a:t>Q=1</a:t>
+            <a:t>Q=2</a:t>
           </a:r>
           <a:endParaRPr b="0" lang="pt-BR" sz="2100" spc="-1" strike="noStrike">
             <a:latin typeface="Times New Roman"/>
@@ -2517,8 +3083,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Q22"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.35"/>
@@ -2531,10 +3097,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="17.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10.05"/>
   </cols>
@@ -2858,216 +3424,68 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>4.00669540658801</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>2.31876816168547</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0.230423267256214</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0.102271755857065</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>2276</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>0.0414025212659143</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>23.725834797891</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>10.2271755857065</v>
-      </c>
-      <c r="O7" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q7" s="0" t="s">
-        <v>19</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>6.95140325578268</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>5.40806425051478</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>0.312596767741903</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>2276</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.0460956300121867</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>3.69068541300527</v>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>11.4934890706438</v>
-      </c>
-      <c r="O8" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="P8" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q8" s="0" t="s">
-        <v>20</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>3.00939880807021</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>1.49611991928376</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>0.166661913337861</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>0.0630774783768506</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>2276</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.0310971225673595</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>17.6186291739895</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>6.30774783768506</v>
-      </c>
-      <c r="O9" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="P9" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="0" t="s">
-        <v>19</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>18.6236877813674</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>5.23702281480804</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>0.729396347368384</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>0.1902454150061</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>2276</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>0.123496017975688</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>32.0298769771529</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>19.02454150061</v>
-      </c>
-      <c r="O10" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="P10" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q10" s="0" t="s">
-        <v>20</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -3278,6 +3696,430 @@
         <v>21</v>
       </c>
       <c r="Q14" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q15" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q16" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="N17" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="O17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q17" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q18" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="N19" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="O19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q19" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="K20" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="O20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P20" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q20" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="J21" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="N21" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="O21" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P21" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q21" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>2276</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="N22" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="O22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q22" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3297,9 +4139,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <dimension ref="H29:O29"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="N29" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="O29" s="0" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3316,16 +4170,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="C4:L10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B1:U38"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.24"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="0" t="s">
+        <v>95</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="2"/>
       <c r="D4" s="3" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -3334,61 +4193,61 @@
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="2"/>
       <c r="D5" s="3" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="G5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="2"/>
       <c r="D6" s="4" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.230423267256214</v>
+        <v>0.423259058657071</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.312596767741903</v>
+        <v>0.808131250732036</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.166661913337861</v>
+        <v>0.765708758525855</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.729396347368384</v>
+        <v>1.69662150777022</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.0414025212659143</v>
+        <v>0.0177510096199239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.0460956300121867</v>
+        <v>0.049449831463592</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.0310971225673595</v>
+        <v>0.0592426110108911</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.123496017975688</v>
+        <v>0.121132215577021</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3396,44 +4255,183 @@
         <v>13</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>10.2271755857065</v>
+        <v>7.82621971274329</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>11.4934890706438</v>
+        <v>11.6303586133599</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>6.30774783768506</v>
+        <v>11.6094614988028</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>19.02454150061</v>
+        <v>19.8988980227079</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>23.725834797891</v>
+        <v>23.5500878734622</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>3.69068541300527</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>17.6186291739895</v>
+        <v>19.3321616871705</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>32.0298769771529</v>
+        <v>33.3479789103691</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N24" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="U24" s="0" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U25" s="0" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U26" s="0" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N27" s="0" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N28" s="0" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="0" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="2"/>
+      <c r="D32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="2"/>
+      <c r="D33" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C34" s="2"/>
+      <c r="D34" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C35" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>0.399944736577236</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>0.73953943918402</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>0.735084466293913</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>1.57383095952598</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>0.0144553691959846</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>0.0446090760499173</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>0.0579975173512967</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>0.108120298383683</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>7.39512909975234</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>10.9881858827173</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>5.57996485061511</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>20.8610034176533</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>17.6625659050967</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>2.72407732864675</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>11.227710093578</v>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>11.7311072056239</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -3451,28 +4449,38 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="0" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>38</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J27" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="0" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3493,27 +4501,116 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="0" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>38</v>
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K23" s="0" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J22" s="0" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="0" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3534,7 +4631,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -3553,7 +4650,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:Q20"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.49"/>
@@ -3570,14 +4667,14 @@
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="M3" s="2"/>
       <c r="N3" s="3" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
@@ -3586,54 +4683,54 @@
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="F4" s="3"/>
       <c r="M4" s="2"/>
       <c r="N4" s="3" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="Q4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="4" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.0806540325578527</v>
@@ -3648,7 +4745,7 @@
         <v>0.0810800437887576</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0.0806574981493508</v>
@@ -3665,7 +4762,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.031391166194122</v>
@@ -3680,7 +4777,7 @@
         <v>0.0149610815644011</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0.0314105892444101</v>
@@ -3729,7 +4826,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>30.6766575840145</v>
@@ -3744,7 +4841,7 @@
         <v>28.2356948228883</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="N9" s="5" t="n">
         <v>30.483651226158</v>
@@ -3761,7 +4858,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I13" s="0" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3812,7 +4909,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -3831,22 +4928,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="0" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3867,16 +4964,21 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>39</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H21" s="0" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3897,7 +4999,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -3916,22 +5018,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="0" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3952,11 +5054,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3964,10 +5066,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
